--- a/base/analise-avancada-cartesian.xlsx
+++ b/base/analise-avancada-cartesian.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado 18/04/2026 01:18 . 126 projetos</t>
+          <t>Gerado 18/04/2026 08:26 . 126 projetos</t>
         </is>
       </c>
     </row>
@@ -3694,14 +3694,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CLUSTER_0 — 27 projetos — padrao dom: medio-alto</t>
+          <t>CLUSTER_0 — 32 projetos — padrao dom: medio-alto</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AC mediana: 5,788 m²   |   R$/m² mediana: R$ 3,378.45   |   Mix padroes: {'medio-alto': 18, 'alto': 7, 'economico': 2}</t>
+          <t>AC mediana: 5,183 m²   |   R$/m² mediana: R$ 3,542.23   |   Mix padroes: {'medio-alto': 21, 'alto': 9, 'economico': 2}</t>
         </is>
       </c>
     </row>
@@ -3724,27 +3724,27 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>21.98</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Instalacoes Hidrossanitarias</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>11.37</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Instalacoes Hidrossanitarias</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>10.44</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>9.890000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3764,20 +3764,20 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>9.06</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>CLUSTER_3 — 13 projetos — padrao dom: medio-alto</t>
+          <t>CLUSTER_1 — 9 projetos — padrao dom: medio-alto</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AC mediana: 4,430 m²   |   R$/m² mediana: R$ 3,799.28   |   Mix padroes: {'medio-alto': 9, 'alto': 4}</t>
+          <t>AC mediana: 3,972 m²   |   R$/m² mediana: R$ 5,246.69   |   Mix padroes: {'medio-alto': 5, 'alto': 4}</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>39.55</v>
+        <v>42.47</v>
       </c>
     </row>
     <row r="20">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>15.3</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="21">
@@ -3820,40 +3820,40 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>7.22</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>5.4</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Pisos e Pavimentacoes</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>5.15</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CLUSTER_1 — 9 projetos — padrao dom: medio-alto</t>
+          <t>CLUSTER_2 — 28 projetos — padrao dom: medio-alto</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AC mediana: 10,479 m²   |   R$/m² mediana: R$ 3,455.81   |   Mix padroes: {'medio-alto': 4, 'alto': 4, 'economico': 1}</t>
+          <t>AC mediana: 12,674 m²   |   R$/m² mediana: R$ 3,290.71   |   Mix padroes: {'medio-alto': 16, 'alto': 8, 'medio': 2, 'economico': 1, 'insuficiente': 1}</t>
         </is>
       </c>
     </row>
@@ -3872,64 +3872,64 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>14.39</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>14.03</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Infraestrutura</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>9.31</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Pisos e Pavimentacoes</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Servicos Complementares</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>9</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CLUSTER_2 — 27 projetos — padrao dom: medio-alto</t>
+          <t>CLUSTER_3 — 7 projetos — padrao dom: medio-alto</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AC mediana: 12,519 m²   |   R$/m² mediana: R$ 3,296.10   |   Mix padroes: {'medio-alto': 15, 'alto': 9, 'medio': 2, 'insuficiente': 1}</t>
+          <t>AC mediana: 7,529 m²   |   R$/m² mediana: R$ 3,761.10   |   Mix padroes: {'alto': 3, 'medio-alto': 4}</t>
         </is>
       </c>
     </row>
@@ -3948,51 +3948,51 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Supraestrutura</t>
+          <t>Gerenciamento</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>18.97</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Supraestrutura</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>18.3</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Gerenciamento</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>11.45</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Infraestrutura</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>9.9</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Servicos Complementares</t>
+          <t>Instalacoes Gerais</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>7.48</v>
+        <v>5.67</v>
       </c>
     </row>
   </sheetData>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>amalfi-ravello</t>
+          <t>amalfi-marine</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>353.3296719539406</v>
+        <v>521.7076950240738</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>111266.4413594261</v>
+        <v>27040.58841300018</v>
       </c>
     </row>
     <row r="7">
@@ -4161,24 +4161,24 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>as-ramos-paessaggio</t>
+          <t>amalfi-ravello</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>AS Ramos</t>
+          <t>Amalfi</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>264.0524005847774</v>
+        <v>353.3296719539406</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>129837.94219092</v>
+        <v>111266.4413594261</v>
       </c>
     </row>
     <row r="8">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>brasin-mario-lago</t>
+          <t>as-ramos-paessaggio</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Brasin</t>
+          <t>AS Ramos</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4202,8 +4202,12 @@
           <t>medio-alto</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="E8" s="8" t="n">
+        <v>264.0524005847774</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>129837.94219092</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4213,25 +4217,21 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>brava-construtora-mar-a-vista</t>
+          <t>brasin-mario-lago</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Brava Construtora</t>
+          <t>Brasin</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>563.1398278873736</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>18550.44524055448</v>
-      </c>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4241,21 +4241,25 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>ck-artefacto</t>
+          <t>brava-construtora-mar-a-vista</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>CK</t>
+          <t>Brava Construtora</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="9" t="n"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>563.1398278873736</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>18550.44524055448</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4265,21 +4269,25 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>ck-habitah</t>
+          <t>caledonia-mowe-caledonia-mowe</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>CK</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="9" t="n"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>329.57</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>4864.662517782525</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4289,7 +4297,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>ck-urbe</t>
+          <t>ck-artefacto</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4313,12 +4321,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>cn-brava-garden</t>
+          <t>ck-habitah</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>CN Brava</t>
+          <t>CK</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4337,12 +4345,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>cn-brava-valley</t>
+          <t>ck-urbe</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>CN Brava</t>
+          <t>CK</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -4361,12 +4369,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>fonseca-empreendimentos-estoril</t>
+          <t>cn-brava-garden</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>CN Brava</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -4374,12 +4382,8 @@
           <t>medio-alto</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>14491.98</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>3378.446360574308</v>
-      </c>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4389,12 +4393,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>h-empreendimentos-atlantia</t>
+          <t>cn-brava-valley</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>H Empreendimentos</t>
+          <t>CN Brava</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -4402,12 +4406,8 @@
           <t>medio-alto</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n">
-        <v>288.7994195755723</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>139959.3689728762</v>
-      </c>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>mussi-empreendimentos-brookliin</t>
+          <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Mussi Empreendimentos</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -4430,8 +4430,12 @@
           <t>medio-alto</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="9" t="n"/>
+      <c r="E17" s="8" t="n">
+        <v>14491.98</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>3378.446360574308</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4441,24 +4445,24 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>paludo-urban-life</t>
+          <t>h-empreendimentos-atlantia</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Paludo</t>
+          <t>H Empreendimentos</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>7040.19</v>
+        <v>288.7994195755723</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2624.8</v>
+        <v>139959.3689728762</v>
       </c>
     </row>
     <row r="19">
@@ -4469,12 +4473,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>parkside-trindade</t>
+          <t>kirchner-kirchner</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Parkside</t>
+          <t>Kirchner</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -4482,12 +4486,8 @@
           <t>medio-alto</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
-        <v>3332.96</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>3755.78</v>
-      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>pass-e-barao-de-albuquerque</t>
+          <t>mendes-empreendimentos-brava-mundo</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Pass-e</t>
+          <t>Mendes Empreendimentos</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>6022.06</v>
+        <v>4811.54</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>4344.71</v>
+        <v>4187.673322886229</v>
       </c>
     </row>
     <row r="21">
@@ -4525,25 +4525,21 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>pass-e-belissimo</t>
+          <t>mussi-empreendimentos-brookliin</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Pass-e</t>
+          <t>Mussi Empreendimentos</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>15621.97</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>1983.37</v>
-      </c>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4553,24 +4549,24 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>pass-e-celebration</t>
+          <t>paludo-urban-life</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Pass-e</t>
+          <t>Paludo</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>7956.14</v>
+        <v>7040.19</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>3148.01</v>
+        <v>2624.8</v>
       </c>
     </row>
     <row r="23">
@@ -4581,12 +4577,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>pass-e-connect</t>
+          <t>parkside-trindade</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Pass-e</t>
+          <t>Parkside</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -4595,10 +4591,10 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>13144.27</v>
+        <v>3332.96</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>3709.52</v>
+        <v>3755.78</v>
       </c>
     </row>
     <row r="24">
@@ -4609,7 +4605,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>pass-e-passione</t>
+          <t>pass-e-barao-de-albuquerque</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6681.54</v>
+        <v>6022.06</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>3784.64</v>
+        <v>4344.71</v>
       </c>
     </row>
     <row r="25">
@@ -4637,7 +4633,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>pass-e-vancouver</t>
+          <t>pass-e-belissimo</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -4647,14 +4643,14 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>5554.12</v>
+        <v>15621.97</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2758.48</v>
+        <v>1983.37</v>
       </c>
     </row>
     <row r="26">
@@ -4665,12 +4661,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>rosner-reserva-sao-vicente</t>
+          <t>pass-e-celebration</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Rosner</t>
+          <t>Pass-e</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -4679,10 +4675,10 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>7007.86</v>
+        <v>7956.14</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>3232.2</v>
+        <v>3148.01</v>
       </c>
     </row>
     <row r="27">
@@ -4693,24 +4689,24 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>sak-engenharia</t>
+          <t>pass-e-connect</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Sak</t>
+          <t>Pass-e</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>1700.61</v>
+        <v>13144.27</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>3843.01</v>
+        <v>3709.52</v>
       </c>
     </row>
     <row r="28">
@@ -4721,24 +4717,24 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>santa-maria-feat</t>
+          <t>pass-e-passione</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Santa Maria</t>
+          <t>Pass-e</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>397.6291201777898</v>
+        <v>6681.54</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>141082.0138497831</v>
+        <v>3784.64</v>
       </c>
     </row>
     <row r="29">
@@ -4749,24 +4745,24 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>santa-maria-unimed</t>
+          <t>pass-e-vancouver</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Santa Maria</t>
+          <t>Pass-e</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>52516.04</v>
+        <v>5554.12</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1604.021250507464</v>
+        <v>2758.48</v>
       </c>
     </row>
     <row r="30">
@@ -4777,12 +4773,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>thozen-mirador-de-alicante</t>
+          <t>pavcor</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Thozen</t>
+          <t>Pavcor</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -4791,26 +4787,26 @@
         </is>
       </c>
       <c r="E30" s="8" t="n">
-        <v>474.8275485666585</v>
+        <v>14283.29</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>73777.86906632235</v>
+        <v>3455.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_0</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>all-lago-di-garda</t>
+          <t>rosner-reserva-sao-vicente</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>Rosner</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4819,54 +4815,54 @@
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>7055.73</v>
+        <v>7007.86</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>7159.696096568636</v>
+        <v>3232.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_0</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>gdi-playa-negra</t>
+          <t>sak-engenharia</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>GDI</t>
+          <t>Sak</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>8518.6</v>
+        <v>1700.61</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>4346.61</v>
+        <v>3843.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_0</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>grandezza-gran-royal</t>
+          <t>santa-maria-feat</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Grandezza</t>
+          <t>Santa Maria</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -4875,54 +4871,54 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>5225.33</v>
+        <v>397.6291201777898</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1917.590191196467</v>
+        <v>141082.0138497831</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_0</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>inbrasul-aguas-de-marco</t>
+          <t>santa-maria-unimed</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Inbrasul</t>
+          <t>Santa Maria</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6538.41</v>
+        <v>52516.04</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>3722.92</v>
+        <v>1604.021250507464</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_0</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>inbrasul-opus</t>
+          <t>thozen-mirador-de-alicante</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Inbrasul</t>
+          <t>Thozen</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -4931,26 +4927,26 @@
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>4410.5</v>
+        <v>474.8275485666585</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3799.28</v>
+        <v>73777.86906632235</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>nova-empreendimentos-domus</t>
+          <t>all-lago-di-garda</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Nova Empreendimentos</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -4959,21 +4955,21 @@
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>5009</v>
+        <v>7055.73</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>7668.2</v>
+        <v>7159.696096568636</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>nova-empreendimentos-evora</t>
+          <t>nova-empreendimentos-domus</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -4983,25 +4979,25 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>3477.2</v>
+        <v>5009</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>6123.12</v>
+        <v>7668.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>nova-empreendimentos-malaga</t>
+          <t>nova-empreendimentos-evora</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5015,21 +5011,21 @@
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>4430.32</v>
+        <v>3477.2</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>5246.69</v>
+        <v>6123.12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>nova-empreendimentos-malta</t>
+          <t>nova-empreendimentos-malaga</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5043,49 +5039,49 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>7964.39</v>
+        <v>4430.32</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>6091.07</v>
+        <v>5246.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>paludo-barbados</t>
+          <t>nova-empreendimentos-malta</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Paludo</t>
+          <t>Nova Empreendimentos</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>1728.35</v>
+        <v>7964.39</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>2781.34</v>
+        <v>6091.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>paludo-nassau</t>
+          <t>paludo-barbados</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -5099,21 +5095,21 @@
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>1402.94</v>
+        <v>1728.35</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>2662.81</v>
+        <v>2781.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>paludo-nassau</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5123,25 +5119,25 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E42" s="8" t="n">
-        <v>3972.3</v>
+        <v>1402.94</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>3134.37</v>
+        <v>2662.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>cluster_3</t>
+          <t>cluster_1</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>paludo-volo-ocean</t>
+          <t>paludo-volo-home</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5151,14 +5147,14 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3264.31</v>
+        <v>3972.3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>3650.32</v>
+        <v>3134.37</v>
       </c>
     </row>
     <row r="44">
@@ -5169,12 +5165,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>amalfi-marine</t>
+          <t>paludo-volo-ocean</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Amalfi</t>
+          <t>Paludo</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -5183,54 +5179,50 @@
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>521.7076950240738</v>
+        <v>3264.31</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>27040.58841300018</v>
+        <v>3650.32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>caledonia-mowe-caledonia-mowe</t>
+          <t>carraro-vertice</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Carraro</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>329.57</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>4864.662517782525</v>
-      </c>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>chiquetti-e-dalvesco-atlantis</t>
+          <t>colline-de-france-colline-de-france</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Chiquetti &amp; Dalvesco</t>
+          <t>Colline</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -5238,23 +5230,27 @@
           <t>alto</t>
         </is>
       </c>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="9" t="n"/>
+      <c r="E46" s="8" t="n">
+        <v>27559.45</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>5219.45</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>estilo-condominios-estilo-condominios</t>
+          <t>cota-365</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Estilo Condominios</t>
+          <t>Cota</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -5263,78 +5259,82 @@
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>23967.18</v>
+        <v>17505.56</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>358.35</v>
+        <v>3483.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>kirchner-kirchner</t>
+          <t>dimas-pb2</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Kirchner</t>
+          <t>Dimas</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="9" t="n"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>21215.27</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>4345.32</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>lotisa-serenity</t>
+          <t>estilo-condominios-estilo-condominios</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Lotisa</t>
+          <t>Estilo Condominios</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>economico</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>13606.52</v>
+        <v>23967.18</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>1519.604407298854</v>
+        <v>358.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>mendes-empreendimentos-brava-mundo</t>
+          <t>etr-zion-meridian-tower</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Mendes Empreendimentos</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -5343,26 +5343,26 @@
         </is>
       </c>
       <c r="E50" s="8" t="n">
-        <v>4811.54</v>
+        <v>4617.34</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>4187.673322886229</v>
+        <v>4196.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>pavcor</t>
+          <t>f-nogueira-soberano</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Pavcor</t>
+          <t>F. Nogueira</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -5371,38 +5371,38 @@
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>14283.29</v>
+        <v>27247.73</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>3455.81</v>
+        <v>2634.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>cluster_1</t>
+          <t>cluster_2</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>terrassa-amaro</t>
+          <t>f-nogueira-wpr</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Terrassa</t>
+          <t>F. Nogueira</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E52" s="8" t="n">
-        <v>10479.34</v>
+        <v>37483.31</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>3100.161860683344</v>
+        <v>2549.1</v>
       </c>
     </row>
     <row r="53">
@@ -5413,21 +5413,25 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>carraro-vertice</t>
+          <t>fg-scenarium</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Carraro</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="9" t="n"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>42277.77</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>4888.48</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -5437,24 +5441,24 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>colline-de-france-colline-de-france</t>
+          <t>gmf-moradas-do-atalaia</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Colline</t>
+          <t>Gmf</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E54" s="8" t="n">
-        <v>27559.45</v>
+        <v>7374.18</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>5219.45</v>
+        <v>3481.83</v>
       </c>
     </row>
     <row r="55">
@@ -5465,24 +5469,24 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>cota-365</t>
+          <t>grandezza-gran-tower</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Cota</t>
+          <t>Grandezza</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>17505.56</v>
+        <v>6245.48</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>3483.98</v>
+        <v>3401.76</v>
       </c>
     </row>
     <row r="56">
@@ -5493,24 +5497,24 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>dimas-pb2</t>
+          <t>hacasa-brisa-da-armacao</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Dimas</t>
+          <t>Hacasa</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E56" s="8" t="n">
-        <v>21215.27</v>
+        <v>12828.33</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>4345.32</v>
+        <v>3296.1</v>
       </c>
     </row>
     <row r="57">
@@ -5521,24 +5525,24 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>etr-zion-meridian-tower</t>
+          <t>holze-sense-106</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>Holze</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>4617.34</v>
+        <v>8700</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>4196.73</v>
+        <v>3515.51</v>
       </c>
     </row>
     <row r="58">
@@ -5549,24 +5553,24 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>f-nogueira-soberano</t>
+          <t>libra-concept-libra-conecpt</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>F. Nogueira</t>
+          <t>Libra Concept</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="E58" s="8" t="n">
-        <v>27247.73</v>
+        <v>4338.77</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>2634.07</v>
+        <v>2271.01</v>
       </c>
     </row>
     <row r="59">
@@ -5577,24 +5581,24 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>f-nogueira-wpr</t>
+          <t>lotisa-serenity</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>F. Nogueira</t>
+          <t>Lotisa</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>economico</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>37483.31</v>
+        <v>13606.52</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>2549.1</v>
+        <v>1519.604407298854</v>
       </c>
     </row>
     <row r="60">
@@ -5605,24 +5609,24 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>lumis-live</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>Lumis</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E60" s="8" t="n">
-        <v>42277.77</v>
+        <v>14888.46</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>4888.48</v>
+        <v>2940.01</v>
       </c>
     </row>
     <row r="61">
@@ -5633,12 +5637,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>gmf-moradas-do-atalaia</t>
+          <t>mabrem-gran-torino</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Gmf</t>
+          <t>Mabrem</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -5647,10 +5651,10 @@
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>7374.18</v>
+        <v>12518.96</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>3481.83</v>
+        <v>2974.48</v>
       </c>
     </row>
     <row r="62">
@@ -5661,25 +5665,21 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>grandezza-gran-tower</t>
+          <t>mabrem-san-marino</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Grandezza</t>
+          <t>Mabrem</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>6245.48</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>3401.76</v>
-      </c>
+          <t>insuficiente</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>hacasa-brisa-da-armacao</t>
+          <t>macom-adda</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Hacasa</t>
+          <t>Macom</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>12828.33</v>
+        <v>4358.27</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3296.1</v>
+        <v>3082.6</v>
       </c>
     </row>
     <row r="64">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>holze-sense-106</t>
+          <t>macom-villa-lobos</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Holze</t>
+          <t>Macom</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="E64" s="8" t="n">
-        <v>8700</v>
+        <v>6001.7</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>3515.51</v>
+        <v>2974.22</v>
       </c>
     </row>
     <row r="65">
@@ -5745,24 +5745,24 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>libra-concept-libra-conecpt</t>
+          <t>mtf-m-village-jardim</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Libra Concept</t>
+          <t>MTF</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>4338.77</v>
+        <v>8852.83</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2271.01</v>
+        <v>3732.19</v>
       </c>
     </row>
     <row r="66">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>lumis-live</t>
+          <t>muller-empreendimentos-elleva</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Lumis</t>
+          <t>Muller</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="E66" s="8" t="n">
-        <v>14888.46</v>
+        <v>2969</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>2940.01</v>
+        <v>4358.23</v>
       </c>
     </row>
     <row r="67">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>mabrem-gran-torino</t>
+          <t>muller-empreendimentos-guanabara</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Mabrem</t>
+          <t>Muller</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>12518.96</v>
+        <v>4440.5</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2974.48</v>
+        <v>3228.74</v>
       </c>
     </row>
     <row r="68">
@@ -5829,21 +5829,25 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>mabrem-san-marino</t>
+          <t>mussi-empreendimentos-chelsea</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Mabrem</t>
+          <t>Mussi Empreendimentos</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>insuficiente</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="9" t="n"/>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>15149.39</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>3443.27</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -5853,24 +5857,24 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>macom-adda</t>
+          <t>mussi-empreendimentos-soho</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Macom</t>
+          <t>Mussi Empreendimentos</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>4358.27</v>
+        <v>12000</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>3082.6</v>
+        <v>2455.59</v>
       </c>
     </row>
     <row r="70">
@@ -5881,24 +5885,24 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>macom-villa-lobos</t>
+          <t>neuhaus-botanico</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Macom</t>
+          <t>Neuhaus</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="E70" s="8" t="n">
-        <v>6001.7</v>
+        <v>12953.8</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>2974.22</v>
+        <v>2797.07</v>
       </c>
     </row>
     <row r="71">
@@ -5909,24 +5913,24 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>mtf-m-village-jardim</t>
+          <t>nm-empreendimentos</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>MTF</t>
+          <t>Nm</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>8852.83</v>
+        <v>1540.93</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>3732.19</v>
+        <v>3217.76</v>
       </c>
     </row>
     <row r="72">
@@ -5937,68 +5941,64 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>muller-empreendimentos-elleva</t>
+          <t>nobria</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Muller</t>
+          <t>Nobria</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="E72" s="8" t="n">
-        <v>2969</v>
+        <v>12879.93</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>4358.23</v>
+        <v>3290.71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>muller-empreendimentos-guanabara</t>
+          <t>chiquetti-e-dalvesco-atlantis</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Muller</t>
+          <t>Chiquetti &amp; Dalvesco</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>medio-alto</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>4440.5</v>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>3228.74</v>
-      </c>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>mussi-empreendimentos-chelsea</t>
+          <t>gdi-playa-negra</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Mussi Empreendimentos</t>
+          <t>GDI</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -6007,110 +6007,110 @@
         </is>
       </c>
       <c r="E74" s="8" t="n">
-        <v>15149.39</v>
+        <v>8518.6</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>3443.27</v>
+        <v>4346.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>mussi-empreendimentos-soho</t>
+          <t>grandezza-gran-royal</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Mussi Empreendimentos</t>
+          <t>Grandezza</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>12000</v>
+        <v>5225.33</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>2455.59</v>
+        <v>1917.590191196467</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>neuhaus-botanico</t>
+          <t>inbrasul-aguas-de-marco</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Neuhaus</t>
+          <t>Inbrasul</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E76" s="8" t="n">
-        <v>12953.8</v>
+        <v>6538.41</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>2797.07</v>
+        <v>3722.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>neuhaus-origem</t>
+          <t>inbrasul-opus</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Neuhaus</t>
+          <t>Inbrasul</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>14559.12</v>
+        <v>4410.5</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>4642.46</v>
+        <v>3799.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>nm-empreendimentos</t>
+          <t>neuhaus-origem</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Nm</t>
+          <t>Neuhaus</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -6119,26 +6119,26 @@
         </is>
       </c>
       <c r="E78" s="8" t="n">
-        <v>1540.93</v>
+        <v>14559.12</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>3217.76</v>
+        <v>4642.46</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>cluster_2</t>
+          <t>cluster_3</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>nobria</t>
+          <t>terrassa-amaro</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Nobria</t>
+          <t>Terrassa</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>12879.93</v>
+        <v>10479.34</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>3290.71</v>
+        <v>3100.161860683344</v>
       </c>
     </row>
   </sheetData>
